--- a/conf/config.xlsx
+++ b/conf/config.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
   <si>
     <t>指令类型</t>
   </si>
@@ -61,13 +61,13 @@
     <t>v_bus</t>
   </si>
   <si>
-    <t>connect tsu</t>
+    <t>adb_connect</t>
   </si>
   <si>
     <t>command</t>
   </si>
   <si>
-    <t>ps -ef|grep sysctrl|grep -v grep</t>
+    <t>adb shell " ps -ef|grep sysctrl|grep -v grep "</t>
   </si>
   <si>
     <t>/oemapp/bin/sysctrl</t>
@@ -76,34 +76,58 @@
     <t>指令种类</t>
   </si>
   <si>
+    <t>cat /data/run_info/mcu_ver.txt</t>
+  </si>
+  <si>
+    <t>expected</t>
+  </si>
+  <si>
+    <t>curent/info</t>
+  </si>
+  <si>
+    <t>tsu/raspberry</t>
+  </si>
+  <si>
+    <t>OFF</t>
+  </si>
+  <si>
     <t>get</t>
   </si>
   <si>
-    <t>cat /data/run_info/mcu_ver.txt</t>
-  </si>
-  <si>
-    <t>expected</t>
-  </si>
-  <si>
-    <t>curent/info</t>
-  </si>
-  <si>
-    <t>tsu/raspberry</t>
-  </si>
-  <si>
-    <t>OFF</t>
-  </si>
-  <si>
-    <t>b+/ig/acc/usb</t>
-  </si>
-  <si>
-    <t>on/off</t>
-  </si>
-  <si>
     <t>sleep</t>
   </si>
   <si>
     <t>lpm</t>
+  </si>
+  <si>
+    <t>lpm_out</t>
+  </si>
+  <si>
+    <t>adb shell " cat /etc/cx_version" |grep version|awk -F'=' '{print $2}'"</t>
+  </si>
+  <si>
+    <t>adb shell " cat /data/run_info/mcu_ver.txt"| awk -F' : ' '{print $2}'"</t>
+  </si>
+  <si>
+    <t>adb shell " cat /data/run_info/car_name.txt "</t>
+  </si>
+  <si>
+    <t>adb shell " cat /data/run_info/iccid.txt "</t>
+  </si>
+  <si>
+    <t>adb shell " cat /data/run_info/imei.txt "</t>
+  </si>
+  <si>
+    <t>adb shell " cat /data/run_info/imsi.txt "</t>
+  </si>
+  <si>
+    <t>adb shell " cat /usrdata/conf/tsu_part_num.txt "</t>
+  </si>
+  <si>
+    <t>adb shell " ifconfig |grep wifi"</t>
+  </si>
+  <si>
+    <t>wifi</t>
   </si>
 </sst>
 </file>
@@ -1034,11 +1058,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22.5454545454545" customWidth="1"/>
-    <col min="2" max="2" width="34.2272727272727" customWidth="1"/>
+    <col min="2" max="2" width="47.9" customWidth="1"/>
     <col min="3" max="3" width="23.0909090909091" customWidth="1"/>
     <col min="4" max="4" width="8.53636363636364" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
@@ -1132,20 +1156,19 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>18</v>
-      </c>
-      <c r="H8"/>
-      <c r="I8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1153,19 +1176,16 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
         <v>20</v>
       </c>
-      <c r="F9" t="s">
-        <v>4</v>
-      </c>
       <c r="G9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1173,16 +1193,13 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1190,13 +1207,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1204,10 +1218,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="D12">
+        <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1215,10 +1229,10 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D13">
-        <v>600</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1254,7 +1268,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1265,12 +1279,82 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>23</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
